--- a/review-tasks/1b-testcase-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1b-testcase-review/jury/scoring-sheet.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>указано неверное название кнопки</t>
+          <t>указано неверное название кнопки. Засчитываем и за шаг 5 («Нажать «Ок»»)</t>
         </is>
       </c>
     </row>
@@ -3467,22 +3467,22 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 3, ожидаемый результат</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BIQ</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>У шага нет ожидаемого результата, а это проверка кнопки из С2</t>
+          <t>При дубле по паспорту новая карточка не создаётся (П2.1): повторное «Сохранить» снова даёт С2. «Черновик» бывает только по П5.2</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>сказано, что нет ОР</t>
+          <t>сказано, что карточка не должна сохраниться или черновика быть не должно</t>
         </is>
       </c>
     </row>
@@ -3499,22 +3499,22 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4, ожидаемый результат</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>BIQ</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>«Отмена» закрывает анкету без сохранения, карточка не создаётся (П1.1). «Черновик» бывает только по П5.2</t>
+          <t>У шага нет ожидаемого результата, а это проверка кнопки из С2</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>сказано, что черновика быть не должно</t>
+          <t>сказано, что нет ОР</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Совпадение со списком само по себе не требует контролёра (BIQ-90103, П4.3), карточка сохраняется сразу (П5.1).</t>
+          <t>Совпадение со списком само по себе не требует контролёра (BIQ-90103, П4.3), карточка сохраняется сразу (П5.1). Если участник пишет только про кнопку «Ок» в тексте шага — это Д417.3, не ловушка</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">

--- a/review-tasks/1b-testcase-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1b-testcase-review/jury/scoring-sheet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/review-tasks/1b-testcase-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1b-testcase-review/jury/scoring-sheet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/review-tasks/1b-testcase-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1b-testcase-review/jury/scoring-sheet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,7 +438,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,7 +474,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>0 или 1</t>
+          <t>Найден (1/0)</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,12 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>Ставим 1, если участник предлагает «исправить» это место. Если сам объяснил, почему место верно, — 0. Каждая ловушка −2 балла</t>
+          <t>Ставим 1, если участник считает это место ошибкой. Если сам объяснил, почему место верно, — 0. Каждая ловушка −2 балла</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>Попался (1/0)</t>
         </is>
       </c>
     </row>

--- a/review-tasks/1b-testcase-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1b-testcase-review/jury/scoring-sheet.xlsx
@@ -661,12 +661,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>«Открытие вклада «Надёжный»» не говорит, что проверяется: минимальная сумма и исполнение без контролёра</t>
+          <t>Название обещает отказ при сумме ниже минимальной, но шаги проверяют успешное открытие на минимальной сумме 10 000,00 ₽</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>сказано, что наименование не отражает цель кейса</t>
+          <t>сказано, что название противоречит данным и ожидаемому успешному открытию</t>
         </is>
       </c>
     </row>
@@ -907,22 +907,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5, тестовые данные</t>
+          <t>Шаг 5, ожидаемый результат</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>BIQ</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>500,00 — значение внутри класса. Граница — 999,99: на ней ошибка разработчика (сравнение «≤» вместо «&lt;») видна</t>
+          <t>При введённых 500,00 ₽ требуется С3 «Минимальная сумма для вклада «Пополняемый» — 1 000,00 ₽» (П3.2), а не «Введите сумму вклада». Само значение 500,00 допустимо для класса ниже минимума</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>сказано, что нужно проверять значение у границы (999,99), а не 500,00</t>
+          <t>указано неверное сообщение на сумме 500,00 или приведён текст С3; требование заменить 500,00 на 999,99 само по себе не засчитываем</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>сказано, что на 1 000,00 сообщения быть не должно и «Далее» активна</t>
+          <t>сказано, что на 1 000,00 сообщения о минимальной сумме быть не должно. Активность «Далее» не требуем: остальные обязательные параметры здесь ещё не заданы</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>«Открытие вклада клиенту с FATCA» — не сказано, что проверяется подтверждение контролёром для резидента США при сумме ниже порога</t>
+          <t>Название описывает клиента, не являющегося резидентом США, но в предусловиях указан налоговый резидент США и проверяется его обязательный контроль</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>сказано, что наименование не отражает цель</t>
+          <t>сказано, что название противоречит FATCA-статусу клиента и проверяемому сценарию</t>
         </is>
       </c>
     </row>
@@ -1451,22 +1451,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 3</t>
+          <t>Предусловие 3, ожидаемый результат</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>BIQ</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Оформление заявки — действие в предусловиях, без проверок. Ошибка на этом этапе не будет видна</t>
+          <t>После подписания заявки на 2 500 000,00 ₽ её статус «На подтверждении» (П5.1), не «Исполнена». Исполненную заявку контролёр отклонять не может. Создание исходной заявки в подготовке допустимо</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>сказано, что действие (оформление заявки) лежит в предусловиях</t>
+          <t>указан неверный исходный статус или необходимость подготовить заявку «На подтверждении»; размещение подготовки заявки в предусловиях само по себе не засчитываем</t>
         </is>
       </c>
     </row>
@@ -1611,22 +1611,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2, тестовые данные</t>
+          <t>Шаг 8, ожидаемый результат</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>BIQ</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Остаток 1 500,00 ₽ — значение внутри класса «больше нуля». Граница правила «остаток равен 0,00» — 0,01 ₽</t>
+          <t>После исполнения закрытия счёт получает статус «Закрыт» (П2.3), а кейс ожидает «Открыт». Остаток 1 500,00 ₽ счёта А допустим для отрицательного класса</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>сказано, что для отказа нужно брать остаток у границы (0,01 ₽)</t>
+          <t>указан неверный конечный статус счёта Б; требование заменить 1 500,00 на 0,01 само по себе не засчитываем</t>
         </is>
       </c>
     </row>
@@ -1803,22 +1803,22 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>BIQ</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>«Напротив любого вклада» — у клиента могут быть разные вклады, кейс нужен для конкретного</t>
+          <t>Для вклада нужна операция «Закрыть вклад» (П1.1). «Закрыть счёт» относится к текущему счёту и недоступна в операциях вклада</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>сказано про «любой»: вклад должен быть задан однозначно</t>
+          <t>сказано, что выбран неверный пункт операции или нужно выбрать «Закрыть вклад»</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>«Закрытие вклада совершеннолетнему клиенту» не говорит о цели — граница 18 лет и электронное подписание</t>
+          <t>Название описывает несовершеннолетнего, но в предусловиях клиенту сегодня 18 лет: он совершеннолетний (П5.1), представитель не нужен</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>сказано, что наименование не отражает цель</t>
+          <t>сказано, что название противоречит возрасту и сценарию; требование представителя для этого клиента — ловушка Л4</t>
         </is>
       </c>
     </row>
@@ -3253,12 +3253,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>10.05.2015 — 11 лет, значение внутри класса. Граница — «14 лет исполнится завтра»</t>
+          <t>Название обещает проверку границы 14 лет, но ближайшая точка перед ней — «14 лет исполнится завтра» — не проверяется. Дата 10.05.2015 лежит внутри класса младше 14 лет; для обычной проверки этого класса она допустима</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>сказано, что нужно проверять у границы</t>
+          <t>сказано, что в заявленной проверке границы отсутствует ближайшая точка перед 14-летием; замечание о недопустимости любого значения внутри класса не засчитываем</t>
         </is>
       </c>
     </row>
@@ -3371,22 +3371,22 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 3</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>BIQ</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Нажатие «Создать клиента» — действие в предусловиях</t>
+          <t>Поле «Гражданство» содержит «РФ» и доступно только для чтения (BIQ-90103, состав анкеты). Выбрать в нём значение нельзя. Открытие анкеты в подготовке допустимо</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>сказано, что действие лежит в предусловиях</t>
+          <t>сказано, что поле «Гражданство» нельзя редактировать или выбирать в нём значение; открытие формы в предусловиях само по себе не засчитываем</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>сказано про зависимость от другого кейса или про то, что нет данных существующего клиента. Засчитываем и замечание, что в шаге 8 не указаны данные клиента-двойника. Засчитываем, если замечание написано у 900420 или у 900415</t>
+          <t>сказано про зависимость от другого кейса или про то, что нет данных существующего клиента. Засчитываем и замечание, что в шаге 8 не указаны данные клиента-двойника. Засчитываем только замечание к 900420</t>
         </is>
       </c>
     </row>
